--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -884,7 +884,7 @@
 </t>
   </si>
   <si>
-    <t>Durchgeführte Abgabe eines Arzneimittels mit oder ohne Bezug zur geplanten Abgabe. Verwendet R5 Backport Extensions.</t>
+    <t>Dispensing a medication to a named patient</t>
   </si>
   <si>
     <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="313">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -427,7 +427,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt der Erstellung des Bundles.</t>
+    <t>When the bundle was assembled</t>
   </si>
   <si>
     <t>The date/time that the bundle was assembled - i.e. when the resources were placed in the bundle.</t>
@@ -866,6 +866,12 @@
   </si>
   <si>
     <t>Bundle.entry:durchgefuehrteAbgaben.modifierExtension</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>Bundle.entry:durchgefuehrteAbgaben.link</t>
@@ -1835,7 +1841,7 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -2275,7 +2281,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2288,13 +2294,13 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>21</v>
@@ -2519,7 +2525,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3202,7 +3208,7 @@
         <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
@@ -6803,7 +6809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>265</v>
       </c>
@@ -6824,7 +6830,7 @@
         <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7152,14 +7158,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7174,17 +7180,13 @@
         <v>157</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7250,7 +7252,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -7261,7 +7263,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>184</v>
@@ -7275,7 +7277,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7287,7 +7289,7 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>185</v>
@@ -7371,9 +7373,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>187</v>
@@ -7384,13 +7386,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -7402,7 +7404,7 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>189</v>
@@ -7487,7 +7489,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>191</v>
@@ -7513,13 +7515,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7588,7 +7590,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -7599,7 +7601,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>195</v>
@@ -7711,7 +7713,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>199</v>
@@ -7823,7 +7825,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>200</v>
@@ -7937,7 +7939,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>201</v>
@@ -8053,7 +8055,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>202</v>
@@ -8167,7 +8169,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>208</v>
@@ -8279,9 +8281,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>213</v>
@@ -8292,13 +8294,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
@@ -8393,7 +8395,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>217</v>
@@ -8505,7 +8507,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>218</v>
@@ -8619,21 +8621,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>219</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -8648,17 +8650,13 @@
         <v>157</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -8724,7 +8722,7 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
@@ -8733,9 +8731,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>220</v>
@@ -8752,7 +8750,7 @@
         <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -8779,7 +8777,7 @@
         <v>21</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>21</v>
@@ -8845,9 +8843,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>225</v>
@@ -8864,7 +8862,7 @@
         <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
@@ -8893,7 +8891,7 @@
         <v>21</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>21</v>
@@ -8961,7 +8959,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>229</v>
@@ -9073,7 +9071,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>232</v>
@@ -9185,7 +9183,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>234</v>
@@ -9297,7 +9295,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>237</v>
@@ -9409,7 +9407,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>240</v>
@@ -9521,7 +9519,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>244</v>
@@ -9633,7 +9631,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>245</v>
@@ -9747,7 +9745,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -9863,7 +9861,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>247</v>
@@ -9975,7 +9973,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>250</v>
@@ -10087,7 +10085,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>253</v>
@@ -10201,7 +10199,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>257</v>
@@ -10315,7 +10313,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>261</v>
@@ -10429,10 +10427,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10455,19 +10453,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -10516,7 +10514,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,8 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff und besteht aus allen Durchgeführten Abgaben, 
-die gemeinsam geschrieben werden sollen.</t>
+    <t>Profil für das Schreiben des Medikationsplans mit der $dispense-write Operation.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AT ELGA e-Medikation Transaction Bundle durchgeführte Abgaben</t>
+    <t>AT ELGA e-Medikation Transaction Bundle Durchgeführte Abgaben</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="275">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil für das Schreiben des Medikationsplans mit der $dispense-write Operation.</t>
+    <t>Profil für das Schreiben der Durchgeführten Abgaben mit der $dispense-write Operation.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -579,13 +579,6 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:resource}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
 bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
@@ -599,6 +592,12 @@
     <t>Bundle.entry.modifierExtension</t>
   </si>
   <si>
+    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t>Bundle.entry.link</t>
   </si>
   <si>
@@ -611,7 +610,7 @@
     <t>Bundle.entry.fullUrl</t>
   </si>
   <si>
-    <t>URI for resource (Absolute URL server address or URI for UUID/OID)</t>
+    <t xml:space="preserve">Eindeutige URL für den Eintrag im Bundle. </t>
   </si>
   <si>
     <t>The Absolute URL for the resource.  The fullUrl SHALL NOT disagree with the id in the resource - i.e. if the fullUrl is not a urn:uuid, the URL shall be version-independent URL consistent with the Resource.id. The fullUrl is a version independent reference to the resource. The fullUrl element SHALL have a value except that: 
@@ -626,222 +625,235 @@
     <t>Bundle.entry.resource</t>
   </si>
   <si>
+    <t xml:space="preserve">MedicationDispense {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medicationdispense-durchgefuehrteabgabe}
+</t>
+  </si>
+  <si>
+    <t>Dispensing a medication to a named patient</t>
+  </si>
+  <si>
+    <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>
+  </si>
+  <si>
+    <t>Supply[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search</t>
+  </si>
+  <si>
+    <t>Search related information</t>
+  </si>
+  <si>
+    <t>Information about the search process that lead to the creation of this entry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bdl-2
+</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.mode</t>
+  </si>
+  <si>
+    <t>match | include | outcome - why this is in the result set</t>
+  </si>
+  <si>
+    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
+  </si>
+  <si>
+    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.search.score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Search ranking (between 0 and 1)</t>
+  </si>
+  <si>
+    <t>When searching, the server's search ranking score for the entry.</t>
+  </si>
+  <si>
+    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
+See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request</t>
+  </si>
+  <si>
+    <t>Additional execution information (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bdl-3
+</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.method</t>
+  </si>
+  <si>
+    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
+  </si>
+  <si>
+    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.url</t>
+  </si>
+  <si>
+    <t>URL for HTTP equivalent of this entry</t>
+  </si>
+  <si>
+    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
+  </si>
+  <si>
+    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
+  </si>
+  <si>
+    <t>MedicationDispense</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>For managing cache currency</t>
+  </si>
+  <si>
+    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifMatch</t>
+  </si>
+  <si>
+    <t>For managing update contention</t>
+  </si>
+  <si>
+    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
+  </si>
+  <si>
+    <t>Bundle.entry.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>For conditional creates</t>
+  </si>
+  <si>
+    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response</t>
+  </si>
+  <si>
+    <t>Results of execution (transaction/batch/history)</t>
+  </si>
+  <si>
+    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bdl-4
+</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.status</t>
+  </si>
+  <si>
+    <t>Status response code (text optional)</t>
+  </si>
+  <si>
+    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.location</t>
+  </si>
+  <si>
+    <t>The location (if the operation returns a location)</t>
+  </si>
+  <si>
+    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.etag</t>
+  </si>
+  <si>
+    <t>The Etag for the resource (if relevant)</t>
+  </si>
+  <si>
+    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
+  </si>
+  <si>
+    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.lastModified</t>
+  </si>
+  <si>
+    <t>Server's date time modified</t>
+  </si>
+  <si>
+    <t>The date/time that the resource was modified on the server.</t>
+  </si>
+  <si>
+    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
+  </si>
+  <si>
+    <t>Bundle.entry.response.outcome</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resource
 </t>
   </si>
   <si>
-    <t>A resource in the bundle</t>
-  </si>
-  <si>
-    <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search</t>
-  </si>
-  <si>
-    <t>Search related information</t>
-  </si>
-  <si>
-    <t>Information about the search process that lead to the creation of this entry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bdl-2
-</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.mode</t>
-  </si>
-  <si>
-    <t>match | include | outcome - why this is in the result set</t>
-  </si>
-  <si>
-    <t>Why this entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>There is only one mode. In some corner cases, a resource may be included because it is both a match and an include. In these circumstances, 'match' takes precedence.</t>
-  </si>
-  <si>
-    <t>Why an entry is in the result set - whether it's included as a match or because of an _include requirement, or to convey information or warning information about the search process.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/search-entry-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.search.score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Search ranking (between 0 and 1)</t>
-  </si>
-  <si>
-    <t>When searching, the server's search ranking score for the entry.</t>
-  </si>
-  <si>
-    <t>Servers are not required to return a ranking score. 1 is most relevant, and 0 is least relevant. Often, search results are sorted by score, but the client may specify a different sort order.
-See [Patient Match](http://hl7.org/fhir/R4/patient-operation-match.html) for the EMPI search which relates to this element.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request</t>
-  </si>
-  <si>
-    <t>Additional execution information (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bdl-3
-</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.method</t>
-  </si>
-  <si>
-    <t>GET | HEAD | POST | PUT | DELETE | PATCH</t>
-  </si>
-  <si>
-    <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
-  </si>
-  <si>
-    <t>HTTP verbs (in the HTTP command line). See [HTTP rfc](https://tools.ietf.org/html/rfc7231) for details.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/http-verb|4.0.1</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.url</t>
-  </si>
-  <si>
-    <t>URL for HTTP equivalent of this entry</t>
-  </si>
-  <si>
-    <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
-  </si>
-  <si>
-    <t>E.g. for a Patient Create, the method would be "POST" and the URL would be "Patient". For a Patient Update, the method would be PUT and the URL would be "Patient/[id]".</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>For managing cache currency</t>
-  </si>
-  <si>
-    <t>If the ETag values match, return a 304 Not Modified status. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifMatch</t>
-  </si>
-  <si>
-    <t>For managing update contention</t>
-  </si>
-  <si>
-    <t>Only perform the operation if the Etag value matches. For more information, see the API section ["Managing Resource Contention"](http://hl7.org/fhir/R4/http.html#concurrency).</t>
-  </si>
-  <si>
-    <t>Bundle.entry.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>For conditional creates</t>
-  </si>
-  <si>
-    <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response</t>
-  </si>
-  <si>
-    <t>Results of execution (transaction/batch/history)</t>
-  </si>
-  <si>
-    <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bdl-4
-</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.status</t>
-  </si>
-  <si>
-    <t>Status response code (text optional)</t>
-  </si>
-  <si>
-    <t>The status code returned by processing this entry. The status SHALL start with a 3 digit HTTP code (e.g. 404) and may contain the standard HTTP description associated with the status code.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.location</t>
-  </si>
-  <si>
-    <t>The location (if the operation returns a location)</t>
-  </si>
-  <si>
-    <t>The location header created by processing this operation, populated if the operation returns a location.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.etag</t>
-  </si>
-  <si>
-    <t>The Etag for the resource (if relevant)</t>
-  </si>
-  <si>
-    <t>The Etag for the resource, if the operation for the entry produced a versioned resource (see [Resource Metadata and Versioning](http://hl7.org/fhir/R4/http.html#versioning) and [Managing Resource Contention](http://hl7.org/fhir/R4/http.html#concurrency)).</t>
-  </si>
-  <si>
-    <t>Etags match the Resource.meta.versionId. The ETag has to match the version id in the header if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.lastModified</t>
-  </si>
-  <si>
-    <t>Server's date time modified</t>
-  </si>
-  <si>
-    <t>The date/time that the resource was modified on the server.</t>
-  </si>
-  <si>
-    <t>This has to match the same time in the meta header (meta.lastUpdated) if a resource is included.</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.outcome</t>
-  </si>
-  <si>
     <t>OperationOutcome with hints and warnings (for batch/transaction)</t>
   </si>
   <si>
@@ -850,133 +862,6 @@
   <si>
     <t>For a POST/PUT operation, this is the equivalent outcome that would be returned for prefer = operationoutcome - except that the resource is always returned whether or not the outcome is returned.
 This outcome is not used for error responses in batch/transaction, only for hints and warnings. In a batch operation, the error will be in Bundle.entry.response, and for transaction, there will be a single OperationOutcome instead of a bundle in the case of an error.</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben</t>
-  </si>
-  <si>
-    <t>durchgefuehrteAbgaben</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.modifierExtension</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.link</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.fullUrl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eindeutige URL für den Eintrag im Bundle. </t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MedicationDispense {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medicationdispense-durchgefuehrteabgabe}
-</t>
-  </si>
-  <si>
-    <t>Dispensing a medication to a named patient</t>
-  </si>
-  <si>
-    <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>
-  </si>
-  <si>
-    <t>Supply[moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.search</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.search.mode</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.search.score</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.method</t>
-  </si>
-  <si>
-    <t>POST</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.url</t>
-  </si>
-  <si>
-    <t>MedicationDispense</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.ifMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response.status</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response.location</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response.etag</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response.lastModified</t>
-  </si>
-  <si>
-    <t>Bundle.entry:durchgefuehrteAbgaben.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -1320,12 +1205,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN81"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.44140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.44140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.09765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3188,7 +3073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>175</v>
       </c>
@@ -3261,14 +3146,16 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>175</v>
@@ -3283,7 +3170,7 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
@@ -3300,10 +3187,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3412,10 +3299,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3526,21 +3413,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3555,17 +3442,13 @@
         <v>157</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3631,7 +3514,7 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -3668,7 +3551,7 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>185</v>
@@ -3752,7 +3635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>187</v>
       </c>
@@ -3765,13 +3648,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
@@ -3879,7 +3762,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>87</v>
@@ -3891,7 +3774,7 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>192</v>
@@ -3969,7 +3852,7 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -3980,10 +3863,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4009,10 +3892,10 @@
         <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4063,7 +3946,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4072,7 +3955,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4092,10 +3975,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4204,10 +4087,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4318,10 +4201,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4434,10 +4317,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4463,13 +4346,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4498,10 +4381,10 @@
         <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4519,7 +4402,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4548,10 +4431,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4574,16 +4457,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4633,7 +4516,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4660,12 +4543,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4673,13 +4556,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -4691,10 +4574,10 @@
         <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4745,7 +4628,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4754,7 +4637,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -4774,10 +4657,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4886,10 +4769,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5000,21 +4883,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5029,17 +4912,13 @@
         <v>157</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5105,7 +4984,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5114,12 +4993,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5133,7 +5012,7 @@
         <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -5145,10 +5024,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5160,7 +5039,7 @@
         <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -5178,10 +5057,10 @@
         <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5199,7 +5078,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5226,12 +5105,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5245,7 +5124,7 @@
         <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5257,13 +5136,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5274,7 +5153,7 @@
         <v>21</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>21</v>
@@ -5313,7 +5192,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5342,10 +5221,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5371,10 +5250,10 @@
         <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5425,7 +5304,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5454,10 +5333,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5483,10 +5362,10 @@
         <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5537,7 +5416,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5566,10 +5445,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5595,10 +5474,10 @@
         <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5649,7 +5528,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5678,10 +5557,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5707,10 +5586,10 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5761,7 +5640,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5790,10 +5669,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5819,10 +5698,10 @@
         <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5873,7 +5752,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5882,7 +5761,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -5902,10 +5781,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6014,10 +5893,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6128,10 +6007,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6244,10 +6123,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6273,10 +6152,10 @@
         <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6327,7 +6206,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6356,10 +6235,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6385,10 +6264,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6439,7 +6318,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6468,10 +6347,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6497,13 +6376,13 @@
         <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6553,7 +6432,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6582,10 +6461,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6611,13 +6490,13 @@
         <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6667,7 +6546,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6696,10 +6575,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6722,16 +6601,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6781,7 +6660,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6808,28 +6687,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -6838,16 +6715,20 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>145</v>
+        <v>270</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>271</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -6895,19 +6776,19 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -6922,3626 +6803,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN81">
+  <autoFilter ref="A1:AN49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10551,7 +6814,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI80">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-durchgefuehrteabgaben-tx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
